--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3204"/>
+  <dimension ref="A1:F3218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -102953,6 +102953,454 @@
         </is>
       </c>
     </row>
+    <row r="3205">
+      <c r="A3205" t="inlineStr">
+        <is>
+          <t>23,Aug</t>
+        </is>
+      </c>
+      <c r="B3205" t="inlineStr">
+        <is>
+          <t>ANMOL KUMAR</t>
+        </is>
+      </c>
+      <c r="C3205" t="inlineStr">
+        <is>
+          <t>ANKUSH KUMAR</t>
+        </is>
+      </c>
+      <c r="D3205" t="inlineStr">
+        <is>
+          <t>DIMPAL KUMARI</t>
+        </is>
+      </c>
+      <c r="E3205" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F3205" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="3206">
+      <c r="A3206" t="inlineStr">
+        <is>
+          <t>23,Aug</t>
+        </is>
+      </c>
+      <c r="B3206" t="inlineStr">
+        <is>
+          <t>AARAV KUMAR</t>
+        </is>
+      </c>
+      <c r="C3206" t="inlineStr">
+        <is>
+          <t>VISHAL KUMAR</t>
+        </is>
+      </c>
+      <c r="D3206" t="inlineStr">
+        <is>
+          <t>RANI KUMARI</t>
+        </is>
+      </c>
+      <c r="E3206" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F3206" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3207">
+      <c r="A3207" t="inlineStr">
+        <is>
+          <t>23,Aug</t>
+        </is>
+      </c>
+      <c r="B3207" t="inlineStr">
+        <is>
+          <t>ADARSH GUPTA</t>
+        </is>
+      </c>
+      <c r="C3207" t="inlineStr">
+        <is>
+          <t>RAMJI PRASAD</t>
+        </is>
+      </c>
+      <c r="D3207" t="inlineStr">
+        <is>
+          <t>NIRMALA DEVI</t>
+        </is>
+      </c>
+      <c r="E3207" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F3207" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3208">
+      <c r="A3208" t="inlineStr">
+        <is>
+          <t>23,Aug</t>
+        </is>
+      </c>
+      <c r="B3208" t="inlineStr">
+        <is>
+          <t>MAYANK KUMAR</t>
+        </is>
+      </c>
+      <c r="C3208" t="inlineStr">
+        <is>
+          <t>SANTOSH KUMAR</t>
+        </is>
+      </c>
+      <c r="D3208" t="inlineStr">
+        <is>
+          <t>BINU SHARMA</t>
+        </is>
+      </c>
+      <c r="E3208" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F3208" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3209">
+      <c r="A3209" t="inlineStr">
+        <is>
+          <t>23,Aug</t>
+        </is>
+      </c>
+      <c r="B3209" t="inlineStr">
+        <is>
+          <t>Annu Priya</t>
+        </is>
+      </c>
+      <c r="C3209" t="inlineStr">
+        <is>
+          <t>Aruna Nand</t>
+        </is>
+      </c>
+      <c r="D3209" t="inlineStr">
+        <is>
+          <t>Renu Kumari</t>
+        </is>
+      </c>
+      <c r="E3209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F3209" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="3210">
+      <c r="A3210" t="inlineStr">
+        <is>
+          <t>23,Aug</t>
+        </is>
+      </c>
+      <c r="B3210" t="inlineStr">
+        <is>
+          <t>ARAV RAJ</t>
+        </is>
+      </c>
+      <c r="C3210" t="inlineStr">
+        <is>
+          <t>GAUTAM KUMAR</t>
+        </is>
+      </c>
+      <c r="D3210" t="inlineStr">
+        <is>
+          <t>NEELU KUMARI</t>
+        </is>
+      </c>
+      <c r="E3210" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F3210" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="3211">
+      <c r="A3211" t="inlineStr">
+        <is>
+          <t>23,Aug</t>
+        </is>
+      </c>
+      <c r="B3211" t="inlineStr">
+        <is>
+          <t>MAIRA TABREZ</t>
+        </is>
+      </c>
+      <c r="C3211" t="inlineStr">
+        <is>
+          <t>MD. TABREZ ALAM</t>
+        </is>
+      </c>
+      <c r="D3211" t="inlineStr">
+        <is>
+          <t>SHAHLA AFRIN</t>
+        </is>
+      </c>
+      <c r="E3211" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F3211" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="3212">
+      <c r="A3212" t="inlineStr">
+        <is>
+          <t>23,Aug</t>
+        </is>
+      </c>
+      <c r="B3212" t="inlineStr">
+        <is>
+          <t>KALPRIT BHARDWAJ</t>
+        </is>
+      </c>
+      <c r="C3212" t="inlineStr">
+        <is>
+          <t>DEEPAK KUMAR</t>
+        </is>
+      </c>
+      <c r="D3212" t="inlineStr">
+        <is>
+          <t>NUTAN KUMARI</t>
+        </is>
+      </c>
+      <c r="E3212" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F3212" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="3213">
+      <c r="A3213" t="inlineStr">
+        <is>
+          <t>23,Aug</t>
+        </is>
+      </c>
+      <c r="B3213" t="inlineStr">
+        <is>
+          <t>VAIBHAV VERMA</t>
+        </is>
+      </c>
+      <c r="C3213" t="inlineStr">
+        <is>
+          <t>VIKASH VERMA</t>
+        </is>
+      </c>
+      <c r="D3213" t="inlineStr">
+        <is>
+          <t>SUPRIYA VERMA</t>
+        </is>
+      </c>
+      <c r="E3213" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F3213" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3214">
+      <c r="A3214" t="inlineStr">
+        <is>
+          <t>23,Aug</t>
+        </is>
+      </c>
+      <c r="B3214" t="inlineStr">
+        <is>
+          <t>DAKSH KUMAR</t>
+        </is>
+      </c>
+      <c r="C3214" t="inlineStr">
+        <is>
+          <t>RAHUL KUMAR</t>
+        </is>
+      </c>
+      <c r="D3214" t="inlineStr">
+        <is>
+          <t>NEHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E3214" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F3214" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="3215">
+      <c r="A3215" t="inlineStr">
+        <is>
+          <t>23,Aug</t>
+        </is>
+      </c>
+      <c r="B3215" t="inlineStr">
+        <is>
+          <t>SAUMYA GAUTAM</t>
+        </is>
+      </c>
+      <c r="C3215" t="inlineStr">
+        <is>
+          <t>UJJWAL KANT GAUTAM</t>
+        </is>
+      </c>
+      <c r="D3215" t="inlineStr">
+        <is>
+          <t>SIMPI DEVI</t>
+        </is>
+      </c>
+      <c r="E3215" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F3215" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="3216">
+      <c r="A3216" t="inlineStr">
+        <is>
+          <t>23,Aug</t>
+        </is>
+      </c>
+      <c r="B3216" t="inlineStr">
+        <is>
+          <t>SAKSHI KUMARI</t>
+        </is>
+      </c>
+      <c r="C3216" t="inlineStr">
+        <is>
+          <t>DHANANJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D3216" t="inlineStr">
+        <is>
+          <t>NIKITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E3216" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F3216" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3217">
+      <c r="A3217" t="inlineStr">
+        <is>
+          <t>23,Aug</t>
+        </is>
+      </c>
+      <c r="B3217" t="inlineStr">
+        <is>
+          <t>RITESH RANJAN KUMAR</t>
+        </is>
+      </c>
+      <c r="C3217" t="inlineStr">
+        <is>
+          <t>RAJEEV RANJAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D3217" t="inlineStr">
+        <is>
+          <t>VINEETA DEVI</t>
+        </is>
+      </c>
+      <c r="E3217" t="inlineStr">
+        <is>
+          <t>XI</t>
+        </is>
+      </c>
+      <c r="F3217" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3218">
+      <c r="A3218" t="inlineStr">
+        <is>
+          <t>23,Aug</t>
+        </is>
+      </c>
+      <c r="B3218" t="inlineStr">
+        <is>
+          <t>Saksham Sharma</t>
+        </is>
+      </c>
+      <c r="C3218" t="inlineStr">
+        <is>
+          <t>Harish Kumar</t>
+        </is>
+      </c>
+      <c r="D3218" t="inlineStr">
+        <is>
+          <t>Soni Kumari</t>
+        </is>
+      </c>
+      <c r="E3218" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F3218" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3218"/>
+  <dimension ref="A1:F3223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -103401,6 +103401,166 @@
         </is>
       </c>
     </row>
+    <row r="3219">
+      <c r="A3219" t="inlineStr">
+        <is>
+          <t>24,Aug</t>
+        </is>
+      </c>
+      <c r="B3219" t="inlineStr">
+        <is>
+          <t>KRISHNA GOSWAMI</t>
+        </is>
+      </c>
+      <c r="C3219" t="inlineStr">
+        <is>
+          <t>RAJA KUMAR</t>
+        </is>
+      </c>
+      <c r="D3219" t="inlineStr">
+        <is>
+          <t>DIVYA KUMARI</t>
+        </is>
+      </c>
+      <c r="E3219" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F3219" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3220">
+      <c r="A3220" t="inlineStr">
+        <is>
+          <t>24,Aug</t>
+        </is>
+      </c>
+      <c r="B3220" t="inlineStr">
+        <is>
+          <t>AASHI KUMARI</t>
+        </is>
+      </c>
+      <c r="C3220" t="inlineStr">
+        <is>
+          <t>ANIL KUMAR</t>
+        </is>
+      </c>
+      <c r="D3220" t="inlineStr">
+        <is>
+          <t>SIMA DEVI</t>
+        </is>
+      </c>
+      <c r="E3220" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F3220" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3221">
+      <c r="A3221" t="inlineStr">
+        <is>
+          <t>24,Aug</t>
+        </is>
+      </c>
+      <c r="B3221" t="inlineStr">
+        <is>
+          <t>Vaibhav Raj</t>
+        </is>
+      </c>
+      <c r="C3221" t="inlineStr">
+        <is>
+          <t>Shailendra Kumar Shail</t>
+        </is>
+      </c>
+      <c r="D3221" t="inlineStr">
+        <is>
+          <t>Anita Kumari</t>
+        </is>
+      </c>
+      <c r="E3221" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F3221" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="3222">
+      <c r="A3222" t="inlineStr">
+        <is>
+          <t>24,Aug</t>
+        </is>
+      </c>
+      <c r="B3222" t="inlineStr">
+        <is>
+          <t>NAMRATA  KUMARI</t>
+        </is>
+      </c>
+      <c r="C3222" t="inlineStr">
+        <is>
+          <t>VIDYA BHUSHAN</t>
+        </is>
+      </c>
+      <c r="D3222" t="inlineStr">
+        <is>
+          <t>PUJA KUMARI</t>
+        </is>
+      </c>
+      <c r="E3222" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F3222" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="3223">
+      <c r="A3223" t="inlineStr">
+        <is>
+          <t>24,Aug</t>
+        </is>
+      </c>
+      <c r="B3223" t="inlineStr">
+        <is>
+          <t>Shubham Kumar</t>
+        </is>
+      </c>
+      <c r="C3223" t="inlineStr">
+        <is>
+          <t>Rajesh Kumar</t>
+        </is>
+      </c>
+      <c r="D3223" t="inlineStr">
+        <is>
+          <t>Anchala Sinha</t>
+        </is>
+      </c>
+      <c r="E3223" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F3223" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3223"/>
+  <dimension ref="A1:F3230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -103561,6 +103561,230 @@
         </is>
       </c>
     </row>
+    <row r="3224">
+      <c r="A3224" t="inlineStr">
+        <is>
+          <t>25,Aug</t>
+        </is>
+      </c>
+      <c r="B3224" t="inlineStr">
+        <is>
+          <t>Nigar  Firdos</t>
+        </is>
+      </c>
+      <c r="C3224" t="inlineStr">
+        <is>
+          <t>Md. Firoz</t>
+        </is>
+      </c>
+      <c r="D3224" t="inlineStr">
+        <is>
+          <t>Shahida Bano</t>
+        </is>
+      </c>
+      <c r="E3224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F3224" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="3225">
+      <c r="A3225" t="inlineStr">
+        <is>
+          <t>25,Aug</t>
+        </is>
+      </c>
+      <c r="B3225" t="inlineStr">
+        <is>
+          <t>SITA KUMARI</t>
+        </is>
+      </c>
+      <c r="C3225" t="inlineStr">
+        <is>
+          <t>JANAK PRASAD</t>
+        </is>
+      </c>
+      <c r="D3225" t="inlineStr">
+        <is>
+          <t>KUSUM DEVI</t>
+        </is>
+      </c>
+      <c r="E3225" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F3225" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3226">
+      <c r="A3226" t="inlineStr">
+        <is>
+          <t>25,Aug</t>
+        </is>
+      </c>
+      <c r="B3226" t="inlineStr">
+        <is>
+          <t>BHAGERATH KUMAR</t>
+        </is>
+      </c>
+      <c r="C3226" t="inlineStr">
+        <is>
+          <t>AVINASH KUMAR</t>
+        </is>
+      </c>
+      <c r="D3226" t="inlineStr">
+        <is>
+          <t>PRITY KUMARI</t>
+        </is>
+      </c>
+      <c r="E3226" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F3226" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="3227">
+      <c r="A3227" t="inlineStr">
+        <is>
+          <t>25,Aug</t>
+        </is>
+      </c>
+      <c r="B3227" t="inlineStr">
+        <is>
+          <t>REYANSH</t>
+        </is>
+      </c>
+      <c r="C3227" t="inlineStr">
+        <is>
+          <t>KUNDAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D3227" t="inlineStr">
+        <is>
+          <t>SIMPI KUMARI</t>
+        </is>
+      </c>
+      <c r="E3227" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F3227" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3228">
+      <c r="A3228" t="inlineStr">
+        <is>
+          <t>25,Aug</t>
+        </is>
+      </c>
+      <c r="B3228" t="inlineStr">
+        <is>
+          <t>Vijaya Kumari</t>
+        </is>
+      </c>
+      <c r="C3228" t="inlineStr">
+        <is>
+          <t>Balmukund Kumar</t>
+        </is>
+      </c>
+      <c r="D3228" t="inlineStr">
+        <is>
+          <t>Ruby Kumari</t>
+        </is>
+      </c>
+      <c r="E3228" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F3228" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="3229">
+      <c r="A3229" t="inlineStr">
+        <is>
+          <t>25,Aug</t>
+        </is>
+      </c>
+      <c r="B3229" t="inlineStr">
+        <is>
+          <t>BHASKAR KUMAR</t>
+        </is>
+      </c>
+      <c r="C3229" t="inlineStr">
+        <is>
+          <t>AVINASH KUMAR</t>
+        </is>
+      </c>
+      <c r="D3229" t="inlineStr">
+        <is>
+          <t>PRITY KUMARI</t>
+        </is>
+      </c>
+      <c r="E3229" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F3229" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3230">
+      <c r="A3230" t="inlineStr">
+        <is>
+          <t>25,Aug</t>
+        </is>
+      </c>
+      <c r="B3230" t="inlineStr">
+        <is>
+          <t>LAKSHYA PRAKASH</t>
+        </is>
+      </c>
+      <c r="C3230" t="inlineStr">
+        <is>
+          <t>RAVI PRAKASH</t>
+        </is>
+      </c>
+      <c r="D3230" t="inlineStr">
+        <is>
+          <t>SITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E3230" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F3230" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
